--- a/Reports/TrendReport_2026-05-14.xlsx
+++ b/Reports/TrendReport_2026-05-14.xlsx
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 14-May-2026 12:54  |  Records: 12  |  Currency: INR (₹)</t>
+          <t>Generated: 14-May-2026 14:01  |  Records: 12  |  Currency: INR (₹)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Average Monthly Total Spend</t>
+          <t>Average Monthly Transactions</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>₹123,956,100</t>
+          <t>3747.50</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>{'Average Transaction Count': '1657', 'Average Transaction Amount': '₹74,778'}</t>
+          <t>{'Maximum Transactions in a Month': '3902', 'Minimum Transactions in a Month': '3533', 'Total Spending for Year': '₹33,850,560,000'}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>1. March and November recorded the highest transaction counts with 1,744 and 1,705 transactions respectively, indicating possible seasonal trends or promotional impacts.</t>
+          <t>1. Transaction count was most stable fluctuating within a range with the maximum difference between months being 369 transactions.</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
@@ -630,7 +630,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2. Total spend peaked in December at ₹133,101,500, suggesting an uptick due to year-end spending.</t>
+          <t>2. Total spending in a month ranged from ₹267,152,000 to ₹298,458,400, showing consistency in customer purchase behavior.</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
@@ -638,7 +638,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>3. The average transaction amount was most stable, with a slight increase reaching a peak in November of ₹76,319.</t>
+          <t>3. The highest total spending occurred alongside the month with the most transactions, indicating a correlation between transaction volume and total spending.</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
@@ -663,13 +663,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -685,12 +684,7 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>total_spend</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>average_transaction_amount</t>
+          <t>total_spent</t>
         </is>
       </c>
     </row>
@@ -701,13 +695,10 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>1712</v>
+        <v>3702</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>129337915.83</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>75547.84803154206</v>
+        <v>279716682.67</v>
       </c>
     </row>
     <row r="3">
@@ -717,13 +708,10 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>1649</v>
+        <v>3533</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>124987424.16</v>
-      </c>
-      <c r="D3" s="6" t="n">
-        <v>75795.89093996362</v>
+        <v>267152011.15</v>
       </c>
     </row>
     <row r="4">
@@ -733,13 +721,10 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1620</v>
+        <v>3810</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>121400658.81</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>74938.67827777778</v>
+        <v>290205115.34</v>
       </c>
     </row>
     <row r="5">
@@ -749,13 +734,10 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>1679</v>
+        <v>3677</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>124036481.47</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>73875.21231089934</v>
+        <v>274114840.46</v>
       </c>
     </row>
     <row r="6">
@@ -765,13 +747,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1675</v>
+        <v>3751</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>127279375.78</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>75987.68703283582</v>
+        <v>282816916.64</v>
       </c>
     </row>
     <row r="7">
@@ -781,13 +760,10 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>1605</v>
+        <v>3645</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>117197978.24</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>73020.54719003115</v>
+        <v>271993581.92</v>
       </c>
     </row>
     <row r="8">
@@ -797,13 +773,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1628</v>
+        <v>3902</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>121678595.76</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>74741.15218673219</v>
+        <v>294520758.88</v>
       </c>
     </row>
     <row r="9">
@@ -813,13 +786,10 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>1630</v>
+        <v>3872</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>119821322.05</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>73510.01352760736</v>
+        <v>298458375.92</v>
       </c>
     </row>
     <row r="10">
@@ -829,13 +799,10 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1681</v>
+        <v>3757</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>123354322.77</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>73381.51265318262</v>
+        <v>276636267.91</v>
       </c>
     </row>
     <row r="11">
@@ -845,13 +812,10 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>1606</v>
+        <v>3853</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>121588623.18</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>75708.98080946451</v>
+        <v>290514019.44</v>
       </c>
     </row>
     <row r="12">
@@ -861,13 +825,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>1660</v>
+        <v>3628</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>123688847.93</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>74511.3541746988</v>
+        <v>268311906.06</v>
       </c>
     </row>
     <row r="13">
@@ -877,13 +838,10 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>1744</v>
+        <v>3840</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>133101451.09</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>76319.6393864679</v>
+        <v>290616085.98</v>
       </c>
     </row>
   </sheetData>
@@ -921,7 +879,7 @@
     <row r="4" ht="50" customHeight="1">
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>The banking transactions show a stable trend throughout 2024, with minor fluctuations in transaction count and total spend. Average transaction values remained consistently around ₹74,778.</t>
+          <t>The trend analysis for 2024 shows a stable transaction pattern with slight variations in monthly volumes and total spending.</t>
         </is>
       </c>
     </row>
@@ -935,8 +893,8 @@
     <row r="7" ht="50" customHeight="1">
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>1. Investigate the factors contributing to the increase in transactions and spending in March and November to replicate them in other months.
-2. Consider customer engagement campaigns in January to boost transaction activity, learning from successful strategies in December.</t>
+          <t>1. Investigate what drove the transaction count and total spending peak in the best performing month to replicate it in other months.
+2. Implement campaigns during months with lower transactions to boost customer engagement and spending.</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1135,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>14-May-2026 12:54</t>
+          <t>14-May-2026 14:01</t>
         </is>
       </c>
     </row>
